--- a/MU/Test upload format/CG fee reduction/2026 - 2027/CP1 26-27.xlsx
+++ b/MU/Test upload format/CG fee reduction/2026 - 2027/CP1 26-27.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>custid</t>
   </si>
@@ -89,19 +89,19 @@
     <t>HomeStay</t>
   </si>
   <si>
-    <t>CR1513</t>
-  </si>
-  <si>
-    <t>10000</t>
+    <t>Q3CRCGFEE02</t>
+  </si>
+  <si>
+    <t>90000</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>40000</t>
-  </si>
-  <si>
-    <t>01-04-2026</t>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>01-12-2026</t>
   </si>
   <si>
     <t>Y</t>
@@ -110,55 +110,10 @@
     <t>01-07-2027</t>
   </si>
   <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>CR1514</t>
+    <t>800000</t>
   </si>
   <si>
     <t>K</t>
-  </si>
-  <si>
-    <t>CR1515</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>CR1516</t>
-  </si>
-  <si>
-    <t>CR1517</t>
-  </si>
-  <si>
-    <t>CR1518</t>
-  </si>
-  <si>
-    <t>CR1519</t>
-  </si>
-  <si>
-    <t>CR1520</t>
-  </si>
-  <si>
-    <t>CR1521</t>
-  </si>
-  <si>
-    <t>CR1522</t>
-  </si>
-  <si>
-    <t>CR1523</t>
-  </si>
-  <si>
-    <t>CR1524</t>
-  </si>
-  <si>
-    <t>CR1512</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
 </sst>
 </file>
@@ -332,7 +287,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,19 +296,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="3" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,7 +638,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -713,16 +662,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -731,87 +680,87 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -823,18 +772,13 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1154,8 +1098,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="24.5714285714286" customWidth="1"/>
@@ -1252,7 +1196,7 @@
       <c r="D2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="8"/>
+      <c r="E2" s="5"/>
       <c r="F2" s="6" t="s">
         <v>23</v>
       </c>
@@ -1262,590 +1206,28 @@
       <c r="H2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="5">
         <v>0</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="5">
         <v>1</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="8" t="s">
         <v>27</v>
       </c>
       <c r="N2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="9" t="s">
         <v>28</v>
       </c>
       <c r="T2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" customFormat="1" spans="1:20">
-      <c r="A3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="8">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8">
-        <v>1</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="T3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" s="8">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8">
-        <v>1</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="T4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
-      <c r="A5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="8">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8">
-        <v>1</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
-      <c r="A6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" s="8">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8">
-        <v>1</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="T6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
-      <c r="A7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8">
-        <v>1</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="T7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
-      <c r="A8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8" s="8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="8">
-        <v>1</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
-      <c r="A9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8">
-        <v>1</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="T9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
-      <c r="A10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="8">
-        <v>0</v>
-      </c>
-      <c r="L10" s="8">
-        <v>1</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="T10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
-      <c r="A11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" s="8">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8">
-        <v>1</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
-      <c r="A12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12" s="8">
-        <v>0</v>
-      </c>
-      <c r="L12" s="8">
-        <v>1</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="T12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
-      <c r="A13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13" s="8">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8">
-        <v>1</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="T13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
-      <c r="A14" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="8">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8">
-        <v>1</v>
-      </c>
-      <c r="M14" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="N14" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="S14" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="T14" t="s">
         <v>22</v>
       </c>
     </row>

--- a/MU/Test upload format/CG fee reduction/2026 - 2027/CP1 26-27.xlsx
+++ b/MU/Test upload format/CG fee reduction/2026 - 2027/CP1 26-27.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
   <si>
     <t>custid</t>
   </si>
@@ -89,31 +89,49 @@
     <t>HomeStay</t>
   </si>
   <si>
-    <t>Q3CRCGFEE02</t>
-  </si>
-  <si>
-    <t>90000</t>
+    <t>Q2CRCGFEE01</t>
+  </si>
+  <si>
+    <t>9000</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>50000</t>
-  </si>
-  <si>
-    <t>01-12-2026</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>01-07-2027</t>
+    <t>01-01-2027</t>
+  </si>
+  <si>
+    <t>900000</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Q2CRCGFEE08</t>
+  </si>
+  <si>
+    <t>9001</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Q2CRCGFEE14</t>
+  </si>
+  <si>
+    <t>9002</t>
   </si>
   <si>
     <t>800000</t>
   </si>
   <si>
-    <t>K</t>
+    <t>Q2CRCGFEE19</t>
+  </si>
+  <si>
+    <t>9003</t>
   </si>
 </sst>
 </file>
@@ -287,7 +305,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -296,13 +314,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.8"/>
+        <fgColor theme="6" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,7 +662,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -662,16 +686,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -680,87 +704,87 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -772,13 +796,18 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1098,8 +1127,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
+  <dimension ref="A1:T5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="17.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="24.5714285714286" customWidth="1"/>
@@ -1137,7 +1166,7 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
@@ -1184,50 +1213,161 @@
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:20">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2"/>
+      <c r="K2" s="6">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6">
+        <v>1</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H2" t="s">
+      <c r="N2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="T2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J2">
+      <c r="B3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="L3" s="6">
         <v>1</v>
       </c>
-      <c r="K2" s="5">
+      <c r="M3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="6">
         <v>0</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L4" s="6">
         <v>1</v>
       </c>
-      <c r="M2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="5" t="s">
+      <c r="M4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6">
+        <v>1</v>
+      </c>
+      <c r="M5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="N5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="T5" t="s">
         <v>22</v>
       </c>
     </row>
